--- a/analysis/tables/ours-1.6b.xlsx
+++ b/analysis/tables/ours-1.6b.xlsx
@@ -495,10 +495,10 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.5497197539314632</v>
+        <v>0.549811321943617</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.03257736857582771</v>
+        <v>-0.03263860220726877</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -506,19 +506,19 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.7101341576805366</v>
+        <v>0.7102506966638465</v>
       </c>
       <c r="H2" t="n">
-        <v>0.08563169728915801</v>
+        <v>0.08562713546898953</v>
       </c>
       <c r="I2" t="n">
-        <v>0.05926177537343751</v>
+        <v>0.0593632777366048</v>
       </c>
       <c r="J2" t="n">
-        <v>0.5171423853556355</v>
+        <v>0.5171727197363483</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1431310929698081</v>
+        <v>0.1431201458234323</v>
       </c>
     </row>
     <row r="3">
@@ -536,30 +536,30 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.8186445272501087</v>
+        <v>0.8636316229808105</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.1044297198695556</v>
+        <v>-0.2916275556923994</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>y = 0.819x - 0.104</t>
+          <t>y = 0.864x - 0.292</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.7940850890904245</v>
+        <v>0.7780498887053863</v>
       </c>
       <c r="H3" t="n">
-        <v>0.07695866535414121</v>
+        <v>0.07711528435831476</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1275641824912007</v>
+        <v>0.3376758654180027</v>
       </c>
       <c r="J3" t="n">
-        <v>0.7142148073805531</v>
+        <v>0.5720040672884111</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1431310929698081</v>
+        <v>0.1431201458234323</v>
       </c>
     </row>
     <row r="4">
@@ -577,30 +577,30 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.8905473972314594</v>
+        <v>0.8539584839846307</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.01134672169303777</v>
+        <v>-0.2785636406273009</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>y = 0.891x - 0.011</t>
+          <t>y = 0.854x - 0.279</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.8476824226826389</v>
+        <v>0.7820202634660472</v>
       </c>
       <c r="H4" t="n">
-        <v>0.07461794539998461</v>
+        <v>0.07694139754119492</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01274128892893578</v>
+        <v>0.3262027907112103</v>
       </c>
       <c r="J4" t="n">
-        <v>0.8792006755384216</v>
+        <v>0.5753948433573298</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1431310929698081</v>
+        <v>0.1431201458234323</v>
       </c>
     </row>
   </sheetData>
